--- a/app/src/main/assets/maestros_reposicion.xlsx
+++ b/app/src/main/assets/maestros_reposicion.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windows\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windows\AndroidStudioProjects\ReposicionInterna\app\src\main\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="466">
   <si>
     <t>Float 6 mm Incoloro</t>
   </si>
@@ -1421,6 +1421,27 @@
   </si>
   <si>
     <t>Ingenieria</t>
+  </si>
+  <si>
+    <t>Laminado</t>
+  </si>
+  <si>
+    <t>Corte</t>
+  </si>
+  <si>
+    <t>DVH</t>
+  </si>
+  <si>
+    <t>Taller</t>
+  </si>
+  <si>
+    <t>Claudia Velazquez</t>
+  </si>
+  <si>
+    <t>Ivan Salva</t>
+  </si>
+  <si>
+    <t>Expedicion</t>
   </si>
 </sst>
 </file>
@@ -1428,10 +1449,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="[$ $]#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$ $]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1442,11 +1463,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -1493,27 +1509,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1808,24 +1821,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>456</v>
       </c>
     </row>
@@ -1833,42 +1846,61 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>458</v>
+      <c r="C3" s="8" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1886,34 +1918,34 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="3"/>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="2"/>
     </row>
     <row r="17" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -3717,7 +3749,7 @@
       </c>
     </row>
     <row r="395" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A395" s="4" t="s">
+      <c r="A395" s="3" t="s">
         <v>367</v>
       </c>
     </row>
@@ -3730,26 +3762,26 @@
       <c r="A397" t="s">
         <v>369</v>
       </c>
-      <c r="B397" s="4"/>
-      <c r="D397" s="4"/>
-      <c r="E397" s="4"/>
-      <c r="F397" s="4"/>
-      <c r="G397" s="4"/>
-      <c r="H397" s="4"/>
-      <c r="I397" s="4"/>
-      <c r="J397" s="4"/>
-      <c r="K397" s="4"/>
-      <c r="L397" s="4"/>
-      <c r="M397" s="4"/>
-      <c r="N397" s="4"/>
-      <c r="O397" s="4"/>
-      <c r="P397" s="4"/>
-      <c r="Q397" s="4"/>
-      <c r="R397" s="4"/>
-      <c r="S397" s="4"/>
-      <c r="T397" s="4"/>
-      <c r="U397" s="4"/>
-      <c r="V397" s="4"/>
+      <c r="B397" s="3"/>
+      <c r="D397" s="3"/>
+      <c r="E397" s="3"/>
+      <c r="F397" s="3"/>
+      <c r="G397" s="3"/>
+      <c r="H397" s="3"/>
+      <c r="I397" s="3"/>
+      <c r="J397" s="3"/>
+      <c r="K397" s="3"/>
+      <c r="L397" s="3"/>
+      <c r="M397" s="3"/>
+      <c r="N397" s="3"/>
+      <c r="O397" s="3"/>
+      <c r="P397" s="3"/>
+      <c r="Q397" s="3"/>
+      <c r="R397" s="3"/>
+      <c r="S397" s="3"/>
+      <c r="T397" s="3"/>
+      <c r="U397" s="3"/>
+      <c r="V397" s="3"/>
     </row>
     <row r="398" spans="1:22" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
